--- a/uploads/Excel/WorkList.xlsx
+++ b/uploads/Excel/WorkList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Title</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -36,35 +36,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>;kjhv </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Anu Hanan</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sadx</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>aa</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rejected</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hello</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>work</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ddddd</t>
+    <t>s;dlfkjvh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>client2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>askdjhfgv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>askdjhcg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -72,43 +56,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>s</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>jhgcaaaaaaaaaaaaaaaaaa</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sds</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://localhost:4200/work</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Approved</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mmm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>,,</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>a</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>aaa</t>
+    <t>alsdkcjhvb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>client3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alsdkjhcgv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alskdjhcb</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -510,100 +470,15 @@
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
